--- a/Plotting/Results_excels/production_shares_ammonia_LowAmbition.xlsx
+++ b/Plotting/Results_excels/production_shares_ammonia_LowAmbition.xlsx
@@ -539,7 +539,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Conventional</t>
+          <t>Conventional (fossil)</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -552,7 +552,7 @@
         <v>-2.620601923793058e-10</v>
       </c>
       <c r="E4" t="n">
-        <v>1184000.000000074</v>
+        <v>1183999.999999923</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -561,7 +561,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>1183999.999999876</v>
+        <v>1184000.000000064</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -573,7 +573,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Carbon Capture</t>
+          <t>Conventional (fossil) with CC</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -623,19 +623,19 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1181739.817836299</v>
+        <v>1181736.586498675</v>
       </c>
       <c r="G6" t="n">
-        <v>1181730.993934782</v>
+        <v>1181730.993934861</v>
       </c>
       <c r="H6" t="n">
-        <v>4.984140500134267e-07</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1181737.653169923</v>
+        <v>1181736.222301789</v>
       </c>
       <c r="J6" t="n">
-        <v>1181730.993934819</v>
+        <v>1181730.993934835</v>
       </c>
     </row>
     <row r="7">
@@ -663,7 +663,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>6.694979318452933e-09</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
